--- a/MIP_RULE/results/random_median_piece_details.xlsx
+++ b/MIP_RULE/results/random_median_piece_details.xlsx
@@ -674,22 +674,22 @@
         <v>15</v>
       </c>
       <c r="I5" t="n">
-        <v>21.15</v>
+        <v>16.5</v>
       </c>
       <c r="J5" t="n">
-        <v>21.15</v>
+        <v>16.5</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>26.97</v>
+        <v>22.32</v>
       </c>
       <c r="M5" t="n">
-        <v>28.8</v>
+        <v>24.15</v>
       </c>
       <c r="N5" t="n">
-        <v>26.97</v>
+        <v>22.32</v>
       </c>
     </row>
     <row r="6">
@@ -770,22 +770,22 @@
         <v>25</v>
       </c>
       <c r="I7" t="n">
-        <v>31.15</v>
+        <v>26.5</v>
       </c>
       <c r="J7" t="n">
-        <v>31.15</v>
+        <v>26.5</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>37.33</v>
+        <v>32.68</v>
       </c>
       <c r="M7" t="n">
-        <v>39.51</v>
+        <v>34.86</v>
       </c>
       <c r="N7" t="n">
-        <v>37.33</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="8">
@@ -818,22 +818,22 @@
         <v>30</v>
       </c>
       <c r="I8" t="n">
-        <v>36.15</v>
+        <v>31.5</v>
       </c>
       <c r="J8" t="n">
-        <v>39.50999999999571</v>
+        <v>34.85999999999571</v>
       </c>
       <c r="K8" t="n">
         <v>3.359999999995708</v>
       </c>
       <c r="L8" t="n">
-        <v>45.68999999999571</v>
+        <v>41.03999999999571</v>
       </c>
       <c r="M8" t="n">
-        <v>47.86999999999571</v>
+        <v>43.21999999999571</v>
       </c>
       <c r="N8" t="n">
-        <v>45.68999999999571</v>
+        <v>41.03999999999571</v>
       </c>
     </row>
     <row r="9">
@@ -866,22 +866,22 @@
         <v>35</v>
       </c>
       <c r="I9" t="n">
-        <v>44.25</v>
+        <v>39.6</v>
       </c>
       <c r="J9" t="n">
-        <v>44.25</v>
+        <v>39.6</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>50.76</v>
+        <v>46.11</v>
       </c>
       <c r="M9" t="n">
-        <v>53.28</v>
+        <v>48.63</v>
       </c>
       <c r="N9" t="n">
-        <v>50.76</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="10">
@@ -1010,22 +1010,22 @@
         <v>50</v>
       </c>
       <c r="I12" t="n">
-        <v>57.7</v>
+        <v>53.05</v>
       </c>
       <c r="J12" t="n">
-        <v>57.7</v>
+        <v>53.05</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>64.01000000000001</v>
+        <v>59.35999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>66.33</v>
+        <v>61.67999999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>64.01000000000001</v>
+        <v>59.35999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1058,22 +1058,22 @@
         <v>55</v>
       </c>
       <c r="I13" t="n">
-        <v>64.25</v>
+        <v>59.6</v>
       </c>
       <c r="J13" t="n">
-        <v>64.25</v>
+        <v>59.6</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>70.56</v>
+        <v>65.91000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>72.88</v>
+        <v>68.23</v>
       </c>
       <c r="N13" t="n">
-        <v>70.56</v>
+        <v>65.91000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1202,22 +1202,22 @@
         <v>70</v>
       </c>
       <c r="I16" t="n">
-        <v>79.25</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>79.25</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>85.43000000000001</v>
+        <v>80.78</v>
       </c>
       <c r="M16" t="n">
-        <v>87.61</v>
+        <v>82.95999999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>85.43000000000001</v>
+        <v>80.78</v>
       </c>
     </row>
     <row r="17">
@@ -1250,22 +1250,22 @@
         <v>75</v>
       </c>
       <c r="I17" t="n">
-        <v>84.25</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>87.60999999999338</v>
+        <v>82.95999999999337</v>
       </c>
       <c r="K17" t="n">
         <v>3.359999999993377</v>
       </c>
       <c r="L17" t="n">
-        <v>92.95</v>
+        <v>88.3</v>
       </c>
       <c r="M17" t="n">
-        <v>94.27999999999338</v>
+        <v>89.62999999999337</v>
       </c>
       <c r="N17" t="n">
-        <v>92.95</v>
+        <v>88.3</v>
       </c>
     </row>
     <row r="18">
@@ -1394,22 +1394,22 @@
         <v>90</v>
       </c>
       <c r="I20" t="n">
-        <v>97.7</v>
+        <v>93.05</v>
       </c>
       <c r="J20" t="n">
-        <v>97.7</v>
+        <v>93.05</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>104.01</v>
+        <v>99.36</v>
       </c>
       <c r="M20" t="n">
-        <v>106.33</v>
+        <v>101.68</v>
       </c>
       <c r="N20" t="n">
-        <v>104.01</v>
+        <v>99.36</v>
       </c>
     </row>
     <row r="21">
@@ -1442,22 +1442,22 @@
         <v>95</v>
       </c>
       <c r="I21" t="n">
-        <v>102.7</v>
+        <v>98.05</v>
       </c>
       <c r="J21" t="n">
-        <v>106.3299999999943</v>
+        <v>101.6799999999943</v>
       </c>
       <c r="K21" t="n">
         <v>3.629999999994254</v>
       </c>
       <c r="L21" t="n">
-        <v>112.1799999999943</v>
+        <v>107.5299999999942</v>
       </c>
       <c r="M21" t="n">
-        <v>114.0199999999943</v>
+        <v>109.3699999999942</v>
       </c>
       <c r="N21" t="n">
-        <v>112.1799999999943</v>
+        <v>107.5299999999942</v>
       </c>
     </row>
     <row r="22">
@@ -1490,22 +1490,22 @@
         <v>100</v>
       </c>
       <c r="I22" t="n">
-        <v>106.15</v>
+        <v>101.5</v>
       </c>
       <c r="J22" t="n">
-        <v>106.15</v>
+        <v>101.5</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>111.66</v>
+        <v>107.01</v>
       </c>
       <c r="M22" t="n">
-        <v>113.18</v>
+        <v>108.53</v>
       </c>
       <c r="N22" t="n">
-        <v>111.66</v>
+        <v>107.01</v>
       </c>
     </row>
     <row r="23">
@@ -1538,22 +1538,22 @@
         <v>105</v>
       </c>
       <c r="I23" t="n">
-        <v>112.7</v>
+        <v>108.05</v>
       </c>
       <c r="J23" t="n">
-        <v>114.0199999999875</v>
+        <v>109.3699999999875</v>
       </c>
       <c r="K23" t="n">
         <v>1.31999999998753</v>
       </c>
       <c r="L23" t="n">
-        <v>120.2</v>
+        <v>115.55</v>
       </c>
       <c r="M23" t="n">
-        <v>122.3799999999875</v>
+        <v>117.7299999999875</v>
       </c>
       <c r="N23" t="n">
-        <v>120.2</v>
+        <v>115.55</v>
       </c>
     </row>
     <row r="24">
@@ -1586,22 +1586,22 @@
         <v>110</v>
       </c>
       <c r="I24" t="n">
-        <v>119.25</v>
+        <v>114.6</v>
       </c>
       <c r="J24" t="n">
-        <v>119.25</v>
+        <v>114.6</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>125.07</v>
+        <v>120.42</v>
       </c>
       <c r="M24" t="n">
-        <v>126.9</v>
+        <v>122.25</v>
       </c>
       <c r="N24" t="n">
-        <v>125.07</v>
+        <v>120.42</v>
       </c>
     </row>
     <row r="25">
@@ -1778,22 +1778,22 @@
         <v>130</v>
       </c>
       <c r="I28" t="n">
-        <v>137.7</v>
+        <v>133.05</v>
       </c>
       <c r="J28" t="n">
-        <v>137.7</v>
+        <v>133.05</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>143.88</v>
+        <v>139.23</v>
       </c>
       <c r="M28" t="n">
-        <v>146.06</v>
+        <v>141.41</v>
       </c>
       <c r="N28" t="n">
-        <v>143.88</v>
+        <v>139.23</v>
       </c>
     </row>
     <row r="29">
@@ -2162,22 +2162,22 @@
         <v>170</v>
       </c>
       <c r="I36" t="n">
-        <v>176.15</v>
+        <v>171.5</v>
       </c>
       <c r="J36" t="n">
-        <v>176.15</v>
+        <v>171.5</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>182</v>
+        <v>177.35</v>
       </c>
       <c r="M36" t="n">
-        <v>183.84</v>
+        <v>179.19</v>
       </c>
       <c r="N36" t="n">
-        <v>189.6899999999901</v>
+        <v>185.0399999999901</v>
       </c>
     </row>
     <row r="37">
@@ -2210,22 +2210,22 @@
         <v>175</v>
       </c>
       <c r="I37" t="n">
-        <v>181.15</v>
+        <v>176.5</v>
       </c>
       <c r="J37" t="n">
-        <v>183.8399999999901</v>
+        <v>179.1899999999901</v>
       </c>
       <c r="K37" t="n">
         <v>2.689999999990107</v>
       </c>
       <c r="L37" t="n">
-        <v>189.6899999999901</v>
+        <v>185.0399999999901</v>
       </c>
       <c r="M37" t="n">
-        <v>191.5299999999901</v>
+        <v>186.8799999999901</v>
       </c>
       <c r="N37" t="n">
-        <v>189.6899999999901</v>
+        <v>185.0399999999901</v>
       </c>
     </row>
     <row r="38">
@@ -2258,22 +2258,22 @@
         <v>180</v>
       </c>
       <c r="I38" t="n">
-        <v>189.25</v>
+        <v>184.6</v>
       </c>
       <c r="J38" t="n">
-        <v>189.25</v>
+        <v>184.6</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>195.76</v>
+        <v>191.11</v>
       </c>
       <c r="M38" t="n">
-        <v>198.28</v>
+        <v>193.63</v>
       </c>
       <c r="N38" t="n">
-        <v>195.76</v>
+        <v>191.11</v>
       </c>
     </row>
     <row r="39">
@@ -2450,22 +2450,22 @@
         <v>200</v>
       </c>
       <c r="I42" t="n">
-        <v>207.7</v>
+        <v>203.05</v>
       </c>
       <c r="J42" t="n">
-        <v>207.7</v>
+        <v>203.05</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>214.21</v>
+        <v>209.56</v>
       </c>
       <c r="M42" t="n">
-        <v>216.73</v>
+        <v>212.08</v>
       </c>
       <c r="N42" t="n">
-        <v>214.21</v>
+        <v>209.56</v>
       </c>
     </row>
     <row r="43">
@@ -2498,22 +2498,22 @@
         <v>205</v>
       </c>
       <c r="I43" t="n">
-        <v>211.15</v>
+        <v>206.5</v>
       </c>
       <c r="J43" t="n">
-        <v>211.15</v>
+        <v>206.5</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>217.66</v>
+        <v>213.01</v>
       </c>
       <c r="M43" t="n">
-        <v>220.18</v>
+        <v>215.53</v>
       </c>
       <c r="N43" t="n">
-        <v>217.66</v>
+        <v>213.01</v>
       </c>
     </row>
     <row r="44">
@@ -2546,22 +2546,22 @@
         <v>210</v>
       </c>
       <c r="I44" t="n">
-        <v>217.7</v>
+        <v>213.05</v>
       </c>
       <c r="J44" t="n">
-        <v>217.7</v>
+        <v>213.05</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>223.52</v>
+        <v>218.87</v>
       </c>
       <c r="M44" t="n">
-        <v>225.35</v>
+        <v>220.7</v>
       </c>
       <c r="N44" t="n">
-        <v>223.52</v>
+        <v>218.87</v>
       </c>
     </row>
     <row r="45">
@@ -2642,22 +2642,22 @@
         <v>220</v>
       </c>
       <c r="I46" t="n">
-        <v>229.25</v>
+        <v>224.6</v>
       </c>
       <c r="J46" t="n">
-        <v>229.25</v>
+        <v>224.6</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>235.56</v>
+        <v>230.91</v>
       </c>
       <c r="M46" t="n">
-        <v>237.88</v>
+        <v>233.23</v>
       </c>
       <c r="N46" t="n">
-        <v>235.56</v>
+        <v>230.91</v>
       </c>
     </row>
     <row r="47">
@@ -2690,22 +2690,22 @@
         <v>225</v>
       </c>
       <c r="I47" t="n">
-        <v>231.15</v>
+        <v>226.5</v>
       </c>
       <c r="J47" t="n">
-        <v>231.15</v>
+        <v>226.5</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>236.97</v>
+        <v>232.32</v>
       </c>
       <c r="M47" t="n">
-        <v>238.8</v>
+        <v>234.15</v>
       </c>
       <c r="N47" t="n">
-        <v>236.97</v>
+        <v>232.32</v>
       </c>
     </row>
     <row r="48">
@@ -2738,22 +2738,22 @@
         <v>230</v>
       </c>
       <c r="I48" t="n">
-        <v>239.25</v>
+        <v>234.6</v>
       </c>
       <c r="J48" t="n">
-        <v>239.25</v>
+        <v>234.6</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>245.56</v>
+        <v>240.91</v>
       </c>
       <c r="M48" t="n">
-        <v>247.88</v>
+        <v>243.23</v>
       </c>
       <c r="N48" t="n">
-        <v>245.56</v>
+        <v>240.91</v>
       </c>
     </row>
     <row r="49">
@@ -2786,22 +2786,22 @@
         <v>235</v>
       </c>
       <c r="I49" t="n">
-        <v>241.15</v>
+        <v>236.5</v>
       </c>
       <c r="J49" t="n">
-        <v>241.15</v>
+        <v>236.5</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>246.49</v>
+        <v>241.84</v>
       </c>
       <c r="M49" t="n">
-        <v>247.82</v>
+        <v>243.17</v>
       </c>
       <c r="N49" t="n">
-        <v>246.49</v>
+        <v>241.84</v>
       </c>
     </row>
     <row r="50">
@@ -2834,22 +2834,22 @@
         <v>240</v>
       </c>
       <c r="I50" t="n">
-        <v>249.25</v>
+        <v>244.6</v>
       </c>
       <c r="J50" t="n">
-        <v>249.25</v>
+        <v>244.6</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>255.1</v>
+        <v>250.45</v>
       </c>
       <c r="M50" t="n">
-        <v>256.94</v>
+        <v>252.29</v>
       </c>
       <c r="N50" t="n">
-        <v>255.1</v>
+        <v>250.45</v>
       </c>
     </row>
     <row r="51">
@@ -2882,22 +2882,22 @@
         <v>245</v>
       </c>
       <c r="I51" t="n">
-        <v>252.7</v>
+        <v>248.05</v>
       </c>
       <c r="J51" t="n">
-        <v>252.7</v>
+        <v>248.05</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>258.21</v>
+        <v>253.56</v>
       </c>
       <c r="M51" t="n">
-        <v>259.73</v>
+        <v>255.08</v>
       </c>
       <c r="N51" t="n">
-        <v>258.21</v>
+        <v>253.56</v>
       </c>
     </row>
     <row r="52">
@@ -3074,22 +3074,22 @@
         <v>265</v>
       </c>
       <c r="I55" t="n">
-        <v>274.25</v>
+        <v>269.6</v>
       </c>
       <c r="J55" t="n">
-        <v>274.25</v>
+        <v>269.6</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>279.76</v>
+        <v>275.11</v>
       </c>
       <c r="M55" t="n">
-        <v>281.28</v>
+        <v>276.63</v>
       </c>
       <c r="N55" t="n">
-        <v>279.76</v>
+        <v>275.11</v>
       </c>
     </row>
     <row r="56">
@@ -3266,22 +3266,22 @@
         <v>285</v>
       </c>
       <c r="I59" t="n">
-        <v>294.25</v>
+        <v>289.6</v>
       </c>
       <c r="J59" t="n">
-        <v>294.25</v>
+        <v>289.6</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>300.76</v>
+        <v>296.11</v>
       </c>
       <c r="M59" t="n">
-        <v>303.28</v>
+        <v>298.63</v>
       </c>
       <c r="N59" t="n">
-        <v>300.76</v>
+        <v>296.11</v>
       </c>
     </row>
     <row r="60">
@@ -3314,22 +3314,22 @@
         <v>290</v>
       </c>
       <c r="I60" t="n">
-        <v>297.7</v>
+        <v>293.05</v>
       </c>
       <c r="J60" t="n">
-        <v>297.7</v>
+        <v>293.05</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>303.55</v>
+        <v>298.9</v>
       </c>
       <c r="M60" t="n">
-        <v>305.39</v>
+        <v>300.74</v>
       </c>
       <c r="N60" t="n">
-        <v>303.55</v>
+        <v>298.9</v>
       </c>
     </row>
     <row r="61">
@@ -3362,22 +3362,22 @@
         <v>295</v>
       </c>
       <c r="I61" t="n">
-        <v>304.25</v>
+        <v>299.6</v>
       </c>
       <c r="J61" t="n">
-        <v>304.25</v>
+        <v>299.6</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>310.56</v>
+        <v>305.91</v>
       </c>
       <c r="M61" t="n">
-        <v>312.88</v>
+        <v>308.23</v>
       </c>
       <c r="N61" t="n">
-        <v>310.56</v>
+        <v>305.91</v>
       </c>
     </row>
     <row r="62">
@@ -3458,22 +3458,22 @@
         <v>305</v>
       </c>
       <c r="I63" t="n">
-        <v>311.15</v>
+        <v>306.5</v>
       </c>
       <c r="J63" t="n">
-        <v>311.15</v>
+        <v>306.5</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>317</v>
+        <v>312.35</v>
       </c>
       <c r="M63" t="n">
-        <v>318.84</v>
+        <v>314.19</v>
       </c>
       <c r="N63" t="n">
-        <v>317</v>
+        <v>312.35</v>
       </c>
     </row>
     <row r="64">
@@ -3698,22 +3698,22 @@
         <v>330</v>
       </c>
       <c r="I68" t="n">
-        <v>337.7</v>
+        <v>333.05</v>
       </c>
       <c r="J68" t="n">
-        <v>337.7</v>
+        <v>333.05</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>344.21</v>
+        <v>339.56</v>
       </c>
       <c r="M68" t="n">
-        <v>346.73</v>
+        <v>342.08</v>
       </c>
       <c r="N68" t="n">
-        <v>344.21</v>
+        <v>339.56</v>
       </c>
     </row>
     <row r="69">
@@ -3746,22 +3746,22 @@
         <v>335</v>
       </c>
       <c r="I69" t="n">
-        <v>341.15</v>
+        <v>336.5</v>
       </c>
       <c r="J69" t="n">
-        <v>341.15</v>
+        <v>336.5</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>347.46</v>
+        <v>342.81</v>
       </c>
       <c r="M69" t="n">
-        <v>349.78</v>
+        <v>345.13</v>
       </c>
       <c r="N69" t="n">
-        <v>347.46</v>
+        <v>342.81</v>
       </c>
     </row>
     <row r="70">
@@ -3842,22 +3842,22 @@
         <v>345</v>
       </c>
       <c r="I71" t="n">
-        <v>351.15</v>
+        <v>346.5</v>
       </c>
       <c r="J71" t="n">
-        <v>351.15</v>
+        <v>346.5</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>357.46</v>
+        <v>352.81</v>
       </c>
       <c r="M71" t="n">
-        <v>359.78</v>
+        <v>355.13</v>
       </c>
       <c r="N71" t="n">
-        <v>357.46</v>
+        <v>352.81</v>
       </c>
     </row>
     <row r="72">
@@ -4034,22 +4034,22 @@
         <v>365</v>
       </c>
       <c r="I75" t="n">
-        <v>371.15</v>
+        <v>366.5</v>
       </c>
       <c r="J75" t="n">
-        <v>371.15</v>
+        <v>366.5</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>377.66</v>
+        <v>373.01</v>
       </c>
       <c r="M75" t="n">
-        <v>380.1799999999999</v>
+        <v>375.53</v>
       </c>
       <c r="N75" t="n">
-        <v>377.66</v>
+        <v>373.01</v>
       </c>
     </row>
     <row r="76">
@@ -4082,22 +4082,22 @@
         <v>370</v>
       </c>
       <c r="I76" t="n">
-        <v>379.25</v>
+        <v>374.6</v>
       </c>
       <c r="J76" t="n">
-        <v>379.25</v>
+        <v>374.6</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>385.07</v>
+        <v>380.42</v>
       </c>
       <c r="M76" t="n">
-        <v>386.9</v>
+        <v>382.25</v>
       </c>
       <c r="N76" t="n">
-        <v>385.07</v>
+        <v>380.42</v>
       </c>
     </row>
     <row r="77">
@@ -4322,22 +4322,22 @@
         <v>395</v>
       </c>
       <c r="I81" t="n">
-        <v>402.7</v>
+        <v>398.05</v>
       </c>
       <c r="J81" t="n">
-        <v>402.7</v>
+        <v>398.05</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>408.52</v>
+        <v>403.87</v>
       </c>
       <c r="M81" t="n">
-        <v>410.35</v>
+        <v>405.7</v>
       </c>
       <c r="N81" t="n">
-        <v>408.52</v>
+        <v>403.87</v>
       </c>
     </row>
     <row r="82">
@@ -4418,22 +4418,22 @@
         <v>405</v>
       </c>
       <c r="I83" t="n">
-        <v>412.7</v>
+        <v>408.05</v>
       </c>
       <c r="J83" t="n">
-        <v>412.7</v>
+        <v>408.05</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>418.04</v>
+        <v>413.39</v>
       </c>
       <c r="M83" t="n">
-        <v>419.37</v>
+        <v>414.72</v>
       </c>
       <c r="N83" t="n">
-        <v>418.04</v>
+        <v>413.39</v>
       </c>
     </row>
     <row r="84">
@@ -4466,22 +4466,22 @@
         <v>410</v>
       </c>
       <c r="I84" t="n">
-        <v>417.7</v>
+        <v>413.05</v>
       </c>
       <c r="J84" t="n">
-        <v>419.3699999999946</v>
+        <v>414.7199999999946</v>
       </c>
       <c r="K84" t="n">
         <v>1.669999999994616</v>
       </c>
       <c r="L84" t="n">
-        <v>425.6799999999946</v>
+        <v>421.0299999999946</v>
       </c>
       <c r="M84" t="n">
-        <v>428</v>
+        <v>423.35</v>
       </c>
       <c r="N84" t="n">
-        <v>425.6799999999946</v>
+        <v>421.0299999999946</v>
       </c>
     </row>
     <row r="85">
@@ -4514,22 +4514,22 @@
         <v>415</v>
       </c>
       <c r="I85" t="n">
-        <v>424.25</v>
+        <v>419.6</v>
       </c>
       <c r="J85" t="n">
-        <v>424.25</v>
+        <v>419.6</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>430.43</v>
+        <v>425.78</v>
       </c>
       <c r="M85" t="n">
-        <v>432.61</v>
+        <v>427.96</v>
       </c>
       <c r="N85" t="n">
-        <v>430.43</v>
+        <v>425.78</v>
       </c>
     </row>
     <row r="86">
@@ -4658,22 +4658,22 @@
         <v>430</v>
       </c>
       <c r="I88" t="n">
-        <v>439.25</v>
+        <v>434.6</v>
       </c>
       <c r="J88" t="n">
-        <v>439.25</v>
+        <v>434.6</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>445.1</v>
+        <v>440.45</v>
       </c>
       <c r="M88" t="n">
-        <v>446.94</v>
+        <v>442.29</v>
       </c>
       <c r="N88" t="n">
-        <v>445.1</v>
+        <v>440.45</v>
       </c>
     </row>
     <row r="89">
@@ -4706,22 +4706,22 @@
         <v>435</v>
       </c>
       <c r="I89" t="n">
-        <v>442.7</v>
+        <v>438.05</v>
       </c>
       <c r="J89" t="n">
-        <v>442.7</v>
+        <v>438.05</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>449.21</v>
+        <v>444.56</v>
       </c>
       <c r="M89" t="n">
-        <v>451.73</v>
+        <v>447.08</v>
       </c>
       <c r="N89" t="n">
-        <v>449.21</v>
+        <v>444.56</v>
       </c>
     </row>
     <row r="90">
@@ -4754,22 +4754,22 @@
         <v>440</v>
       </c>
       <c r="I90" t="n">
-        <v>447.7</v>
+        <v>443.05</v>
       </c>
       <c r="J90" t="n">
-        <v>451.7299999999952</v>
+        <v>447.0799999999952</v>
       </c>
       <c r="K90" t="n">
         <v>4.029999999995198</v>
       </c>
       <c r="L90" t="n">
-        <v>458.0399999999952</v>
+        <v>453.3899999999952</v>
       </c>
       <c r="M90" t="n">
-        <v>460.3599999999952</v>
+        <v>455.7099999999952</v>
       </c>
       <c r="N90" t="n">
-        <v>502.6399999999974</v>
+        <v>497.9899999999974</v>
       </c>
     </row>
     <row r="91">
@@ -4850,22 +4850,22 @@
         <v>450</v>
       </c>
       <c r="I92" t="n">
-        <v>456.15</v>
+        <v>451.5</v>
       </c>
       <c r="J92" t="n">
-        <v>456.15</v>
+        <v>451.5</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
       </c>
       <c r="L92" t="n">
-        <v>462.66</v>
+        <v>458.01</v>
       </c>
       <c r="M92" t="n">
-        <v>465.1799999999999</v>
+        <v>460.53</v>
       </c>
       <c r="N92" t="n">
-        <v>533.95</v>
+        <v>529.3</v>
       </c>
     </row>
     <row r="93">
@@ -4946,22 +4946,22 @@
         <v>460</v>
       </c>
       <c r="I94" t="n">
-        <v>466.15</v>
+        <v>461.5</v>
       </c>
       <c r="J94" t="n">
-        <v>466.15</v>
+        <v>461.5</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
       </c>
       <c r="L94" t="n">
-        <v>472.46</v>
+        <v>467.81</v>
       </c>
       <c r="M94" t="n">
-        <v>474.78</v>
+        <v>470.13</v>
       </c>
       <c r="N94" t="n">
-        <v>507.46</v>
+        <v>502.81</v>
       </c>
     </row>
     <row r="95">
@@ -4994,22 +4994,22 @@
         <v>465</v>
       </c>
       <c r="I95" t="n">
-        <v>471.15</v>
+        <v>466.5</v>
       </c>
       <c r="J95" t="n">
-        <v>474.7799999999974</v>
+        <v>470.1299999999974</v>
       </c>
       <c r="K95" t="n">
         <v>3.629999999997381</v>
       </c>
       <c r="L95" t="n">
-        <v>481.0899999999974</v>
+        <v>476.4399999999974</v>
       </c>
       <c r="M95" t="n">
-        <v>483.4099999999974</v>
+        <v>478.7599999999974</v>
       </c>
       <c r="N95" t="n">
-        <v>516.0899999999973</v>
+        <v>511.4399999999974</v>
       </c>
     </row>
     <row r="96">
@@ -5042,22 +5042,22 @@
         <v>470</v>
       </c>
       <c r="I96" t="n">
-        <v>477.7</v>
+        <v>473.05</v>
       </c>
       <c r="J96" t="n">
-        <v>477.7</v>
+        <v>473.05</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>484.01</v>
+        <v>479.36</v>
       </c>
       <c r="M96" t="n">
-        <v>486.33</v>
+        <v>481.68</v>
       </c>
       <c r="N96" t="n">
-        <v>502.6399999999974</v>
+        <v>497.9899999999974</v>
       </c>
     </row>
     <row r="97">
@@ -5138,22 +5138,22 @@
         <v>480</v>
       </c>
       <c r="I98" t="n">
-        <v>487.7</v>
+        <v>483.05</v>
       </c>
       <c r="J98" t="n">
-        <v>487.7</v>
+        <v>483.05</v>
       </c>
       <c r="K98" t="n">
         <v>0</v>
       </c>
       <c r="L98" t="n">
-        <v>494.01</v>
+        <v>489.36</v>
       </c>
       <c r="M98" t="n">
-        <v>496.33</v>
+        <v>491.68</v>
       </c>
       <c r="N98" t="n">
-        <v>502.6399999999974</v>
+        <v>497.9899999999974</v>
       </c>
     </row>
     <row r="99">
@@ -5186,22 +5186,22 @@
         <v>485</v>
       </c>
       <c r="I99" t="n">
-        <v>492.7</v>
+        <v>488.05</v>
       </c>
       <c r="J99" t="n">
-        <v>496.3299999999974</v>
+        <v>491.6799999999974</v>
       </c>
       <c r="K99" t="n">
         <v>3.629999999997381</v>
       </c>
       <c r="L99" t="n">
-        <v>502.6399999999974</v>
+        <v>497.9899999999974</v>
       </c>
       <c r="M99" t="n">
-        <v>504.9599999999974</v>
+        <v>500.3099999999974</v>
       </c>
       <c r="N99" t="n">
-        <v>502.6399999999974</v>
+        <v>497.9899999999974</v>
       </c>
     </row>
     <row r="100">
@@ -5282,22 +5282,22 @@
         <v>495</v>
       </c>
       <c r="I101" t="n">
-        <v>501.15</v>
+        <v>496.5</v>
       </c>
       <c r="J101" t="n">
-        <v>501.15</v>
+        <v>496.5</v>
       </c>
       <c r="K101" t="n">
         <v>0</v>
       </c>
       <c r="L101" t="n">
-        <v>507.46</v>
+        <v>502.81</v>
       </c>
       <c r="M101" t="n">
-        <v>509.78</v>
+        <v>505.13</v>
       </c>
       <c r="N101" t="n">
-        <v>507.46</v>
+        <v>502.81</v>
       </c>
     </row>
     <row r="102">
@@ -5330,22 +5330,22 @@
         <v>500</v>
       </c>
       <c r="I102" t="n">
-        <v>506.15</v>
+        <v>501.5</v>
       </c>
       <c r="J102" t="n">
-        <v>509.7799999999974</v>
+        <v>505.1299999999974</v>
       </c>
       <c r="K102" t="n">
         <v>3.629999999997381</v>
       </c>
       <c r="L102" t="n">
-        <v>516.0899999999973</v>
+        <v>511.4399999999974</v>
       </c>
       <c r="M102" t="n">
-        <v>518.4099999999974</v>
+        <v>513.7599999999974</v>
       </c>
       <c r="N102" t="n">
-        <v>516.0899999999973</v>
+        <v>511.4399999999974</v>
       </c>
     </row>
     <row r="103">
@@ -5378,22 +5378,22 @@
         <v>505</v>
       </c>
       <c r="I103" t="n">
-        <v>511.15</v>
+        <v>506.5</v>
       </c>
       <c r="J103" t="n">
-        <v>518.4099999999947</v>
+        <v>513.7599999999948</v>
       </c>
       <c r="K103" t="n">
         <v>7.259999999994761</v>
       </c>
       <c r="L103" t="n">
-        <v>524.9199999999947</v>
+        <v>520.2699999999948</v>
       </c>
       <c r="M103" t="n">
-        <v>527.4399999999947</v>
+        <v>522.7899999999947</v>
       </c>
       <c r="N103" t="n">
-        <v>533.95</v>
+        <v>529.3</v>
       </c>
     </row>
     <row r="104">
@@ -5426,22 +5426,22 @@
         <v>510</v>
       </c>
       <c r="I104" t="n">
-        <v>516.15</v>
+        <v>511.5</v>
       </c>
       <c r="J104" t="n">
-        <v>527.4399999999899</v>
+        <v>522.78999999999</v>
       </c>
       <c r="K104" t="n">
         <v>11.28999999998996</v>
       </c>
       <c r="L104" t="n">
-        <v>533.95</v>
+        <v>529.3</v>
       </c>
       <c r="M104" t="n">
-        <v>536.4699999999899</v>
+        <v>531.8199999999899</v>
       </c>
       <c r="N104" t="n">
-        <v>533.95</v>
+        <v>529.3</v>
       </c>
     </row>
   </sheetData>

--- a/MIP_RULE/results/random_median_piece_details.xlsx
+++ b/MIP_RULE/results/random_median_piece_details.xlsx
@@ -503,7 +503,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -521,37 +521,37 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>4.6</v>
+        <v>3.05</v>
       </c>
       <c r="J2" t="n">
-        <v>4.6</v>
+        <v>3.05</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>10.45</v>
+        <v>9.56</v>
       </c>
       <c r="M2" t="n">
-        <v>12.29</v>
+        <v>12.08</v>
       </c>
       <c r="N2" t="n">
-        <v>10.45</v>
+        <v>9.56</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -569,37 +569,37 @@
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
         <v>5</v>
       </c>
       <c r="I3" t="n">
-        <v>8.050000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J3" t="n">
-        <v>8.050000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>13.9</v>
+        <v>15.91</v>
       </c>
       <c r="M3" t="n">
-        <v>15.74</v>
+        <v>18.23</v>
       </c>
       <c r="N3" t="n">
-        <v>13.9</v>
+        <v>15.91</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -617,37 +617,37 @@
         <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>9</v>
+        <v>87</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H4" t="n">
         <v>10</v>
       </c>
       <c r="I4" t="n">
-        <v>11.5</v>
+        <v>14.6</v>
       </c>
       <c r="J4" t="n">
-        <v>11.5</v>
+        <v>14.6</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>18.01</v>
+        <v>20.91</v>
       </c>
       <c r="M4" t="n">
-        <v>20.53</v>
+        <v>23.23</v>
       </c>
       <c r="N4" t="n">
-        <v>18.01</v>
+        <v>20.91</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -665,37 +665,37 @@
         <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
         <v>15</v>
       </c>
       <c r="I5" t="n">
-        <v>16.5</v>
+        <v>19.6</v>
       </c>
       <c r="J5" t="n">
-        <v>16.5</v>
+        <v>23.22999999999425</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>3.629999999994244</v>
       </c>
       <c r="L5" t="n">
-        <v>22.32</v>
+        <v>29.07999999999425</v>
       </c>
       <c r="M5" t="n">
-        <v>24.15</v>
+        <v>30.91999999999425</v>
       </c>
       <c r="N5" t="n">
-        <v>22.32</v>
+        <v>29.07999999999425</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -713,10 +713,10 @@
         <v>4</v>
       </c>
       <c r="F6" t="n">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
         <v>20</v>
@@ -731,19 +731,19 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>28.87</v>
+        <v>29.56</v>
       </c>
       <c r="M6" t="n">
-        <v>30.7</v>
+        <v>32.08</v>
       </c>
       <c r="N6" t="n">
-        <v>28.87</v>
+        <v>29.56</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -761,37 +761,37 @@
         <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
         <v>25</v>
       </c>
       <c r="I7" t="n">
-        <v>26.5</v>
+        <v>28.05</v>
       </c>
       <c r="J7" t="n">
-        <v>26.5</v>
+        <v>32.07999999999206</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>4.029999999992061</v>
       </c>
       <c r="L7" t="n">
-        <v>32.68</v>
+        <v>37.92999999999206</v>
       </c>
       <c r="M7" t="n">
-        <v>34.86</v>
+        <v>39.76999999999206</v>
       </c>
       <c r="N7" t="n">
-        <v>32.68</v>
+        <v>37.92999999999206</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -809,37 +809,37 @@
         <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
         <v>30</v>
       </c>
       <c r="I8" t="n">
-        <v>31.5</v>
+        <v>34.6</v>
       </c>
       <c r="J8" t="n">
-        <v>34.85999999999571</v>
+        <v>34.6</v>
       </c>
       <c r="K8" t="n">
-        <v>3.359999999995708</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>41.03999999999571</v>
+        <v>40.42</v>
       </c>
       <c r="M8" t="n">
-        <v>43.21999999999571</v>
+        <v>42.25</v>
       </c>
       <c r="N8" t="n">
-        <v>41.03999999999571</v>
+        <v>40.42</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -857,37 +857,37 @@
         <v>7</v>
       </c>
       <c r="F9" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="G9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
         <v>35</v>
       </c>
       <c r="I9" t="n">
-        <v>39.6</v>
+        <v>38.05</v>
       </c>
       <c r="J9" t="n">
-        <v>39.6</v>
+        <v>39.7699999999858</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1.719999999985802</v>
       </c>
       <c r="L9" t="n">
-        <v>46.11</v>
+        <v>46.07999999998579</v>
       </c>
       <c r="M9" t="n">
-        <v>48.63</v>
+        <v>48.4</v>
       </c>
       <c r="N9" t="n">
-        <v>46.11</v>
+        <v>46.07999999998579</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -905,37 +905,37 @@
         <v>8</v>
       </c>
       <c r="F10" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
         <v>40</v>
       </c>
       <c r="I10" t="n">
-        <v>43.05</v>
+        <v>44.6</v>
       </c>
       <c r="J10" t="n">
-        <v>43.05</v>
+        <v>44.6</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>48.56</v>
+        <v>50.45</v>
       </c>
       <c r="M10" t="n">
-        <v>50.08</v>
+        <v>52.29</v>
       </c>
       <c r="N10" t="n">
-        <v>48.56</v>
+        <v>50.45</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -953,37 +953,37 @@
         <v>9</v>
       </c>
       <c r="F11" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
         <v>45</v>
       </c>
       <c r="I11" t="n">
-        <v>48.05</v>
+        <v>46.5</v>
       </c>
       <c r="J11" t="n">
-        <v>50.0799999999944</v>
+        <v>46.5</v>
       </c>
       <c r="K11" t="n">
-        <v>2.029999999994402</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>56.38999999999439</v>
+        <v>52.81</v>
       </c>
       <c r="M11" t="n">
-        <v>58.70999999999439</v>
+        <v>55.13</v>
       </c>
       <c r="N11" t="n">
-        <v>56.38999999999439</v>
+        <v>52.81</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1001,37 +1001,37 @@
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="G12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
         <v>50</v>
       </c>
       <c r="I12" t="n">
-        <v>53.05</v>
+        <v>51.5</v>
       </c>
       <c r="J12" t="n">
-        <v>53.05</v>
+        <v>55.1299999999944</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>3.629999999994396</v>
       </c>
       <c r="L12" t="n">
-        <v>59.35999999999999</v>
+        <v>60.63999999999439</v>
       </c>
       <c r="M12" t="n">
-        <v>61.67999999999999</v>
+        <v>62.1599999999944</v>
       </c>
       <c r="N12" t="n">
-        <v>59.35999999999999</v>
+        <v>60.63999999999439</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1049,37 +1049,37 @@
         <v>11</v>
       </c>
       <c r="F13" t="n">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="G13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
         <v>55</v>
       </c>
       <c r="I13" t="n">
-        <v>59.6</v>
+        <v>56.5</v>
       </c>
       <c r="J13" t="n">
-        <v>59.6</v>
+        <v>62.15999999998813</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>5.659999999988131</v>
       </c>
       <c r="L13" t="n">
-        <v>65.91000000000001</v>
+        <v>68.46999999998813</v>
       </c>
       <c r="M13" t="n">
-        <v>68.23</v>
+        <v>70.78999999998813</v>
       </c>
       <c r="N13" t="n">
-        <v>65.91000000000001</v>
+        <v>68.46999999998813</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1097,37 +1097,37 @@
         <v>12</v>
       </c>
       <c r="F14" t="n">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H14" t="n">
         <v>60</v>
       </c>
       <c r="I14" t="n">
-        <v>63.05</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>63.05</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>69.56</v>
+        <v>71.11</v>
       </c>
       <c r="M14" t="n">
-        <v>72.08</v>
+        <v>73.63</v>
       </c>
       <c r="N14" t="n">
-        <v>69.56</v>
+        <v>71.11</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1145,37 +1145,37 @@
         <v>13</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H15" t="n">
         <v>65</v>
       </c>
       <c r="I15" t="n">
-        <v>66.5</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>66.5</v>
+        <v>73.62999999999221</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>4.029999999992214</v>
       </c>
       <c r="L15" t="n">
-        <v>71.84</v>
+        <v>79.13999999999221</v>
       </c>
       <c r="M15" t="n">
-        <v>73.17</v>
+        <v>80.65999999999221</v>
       </c>
       <c r="N15" t="n">
-        <v>71.84</v>
+        <v>79.13999999999221</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1193,37 +1193,37 @@
         <v>14</v>
       </c>
       <c r="F16" t="n">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="G16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>70</v>
       </c>
       <c r="I16" t="n">
-        <v>74.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="J16" t="n">
-        <v>74.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>80.78</v>
+        <v>77.34999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>82.95999999999999</v>
+        <v>79.19</v>
       </c>
       <c r="N16" t="n">
-        <v>80.78</v>
+        <v>77.34999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1241,37 +1241,37 @@
         <v>15</v>
       </c>
       <c r="F17" t="n">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="G17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
         <v>75</v>
       </c>
       <c r="I17" t="n">
-        <v>79.59999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="J17" t="n">
-        <v>82.95999999999337</v>
+        <v>76.5</v>
       </c>
       <c r="K17" t="n">
-        <v>3.359999999993377</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>88.3</v>
+        <v>81.84</v>
       </c>
       <c r="M17" t="n">
-        <v>89.62999999999337</v>
+        <v>83.17</v>
       </c>
       <c r="N17" t="n">
-        <v>88.3</v>
+        <v>81.84</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1289,37 +1289,37 @@
         <v>16</v>
       </c>
       <c r="F18" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
         <v>80</v>
       </c>
       <c r="I18" t="n">
-        <v>83.05</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>83.05</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>89.22999999999999</v>
+        <v>90.78</v>
       </c>
       <c r="M18" t="n">
-        <v>91.41</v>
+        <v>92.95999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>89.22999999999999</v>
+        <v>90.78</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1337,37 +1337,37 @@
         <v>17</v>
       </c>
       <c r="F19" t="n">
-        <v>11</v>
+        <v>89</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H19" t="n">
         <v>85</v>
       </c>
       <c r="I19" t="n">
-        <v>86.5</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>86.5</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>92.81</v>
+        <v>96.11</v>
       </c>
       <c r="M19" t="n">
-        <v>95.13</v>
+        <v>98.63</v>
       </c>
       <c r="N19" t="n">
-        <v>92.81</v>
+        <v>96.11</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1385,37 +1385,37 @@
         <v>18</v>
       </c>
       <c r="F20" t="n">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="G20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H20" t="n">
         <v>90</v>
       </c>
       <c r="I20" t="n">
-        <v>93.05</v>
+        <v>91.5</v>
       </c>
       <c r="J20" t="n">
-        <v>93.05</v>
+        <v>91.5</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>99.36</v>
+        <v>97.68000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>101.68</v>
+        <v>99.86</v>
       </c>
       <c r="N20" t="n">
-        <v>99.36</v>
+        <v>97.68000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1433,37 +1433,37 @@
         <v>19</v>
       </c>
       <c r="F21" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H21" t="n">
         <v>95</v>
       </c>
       <c r="I21" t="n">
-        <v>98.05</v>
+        <v>96.5</v>
       </c>
       <c r="J21" t="n">
-        <v>101.6799999999943</v>
+        <v>99.85999999999396</v>
       </c>
       <c r="K21" t="n">
-        <v>3.629999999994254</v>
+        <v>3.35999999999396</v>
       </c>
       <c r="L21" t="n">
-        <v>107.5299999999942</v>
+        <v>106.369999999994</v>
       </c>
       <c r="M21" t="n">
-        <v>109.3699999999942</v>
+        <v>108.889999999994</v>
       </c>
       <c r="N21" t="n">
-        <v>107.5299999999942</v>
+        <v>106.369999999994</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1481,7 +1481,7 @@
         <v>20</v>
       </c>
       <c r="F22" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G22" t="n">
         <v>3</v>
@@ -1493,25 +1493,25 @@
         <v>101.5</v>
       </c>
       <c r="J22" t="n">
-        <v>101.5</v>
+        <v>108.8899999999872</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>7.389999999987239</v>
       </c>
       <c r="L22" t="n">
-        <v>107.01</v>
+        <v>115.0699999999872</v>
       </c>
       <c r="M22" t="n">
-        <v>108.53</v>
+        <v>117.25</v>
       </c>
       <c r="N22" t="n">
-        <v>107.01</v>
+        <v>115.0699999999872</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1529,10 +1529,10 @@
         <v>21</v>
       </c>
       <c r="F23" t="n">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="G23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
         <v>105</v>
@@ -1541,25 +1541,25 @@
         <v>108.05</v>
       </c>
       <c r="J23" t="n">
-        <v>109.3699999999875</v>
+        <v>108.05</v>
       </c>
       <c r="K23" t="n">
-        <v>1.31999999998753</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>115.55</v>
+        <v>113.39</v>
       </c>
       <c r="M23" t="n">
-        <v>117.7299999999875</v>
+        <v>114.72</v>
       </c>
       <c r="N23" t="n">
-        <v>115.55</v>
+        <v>113.39</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1577,37 +1577,37 @@
         <v>22</v>
       </c>
       <c r="F24" t="n">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="G24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>110</v>
       </c>
       <c r="I24" t="n">
-        <v>114.6</v>
+        <v>111.5</v>
       </c>
       <c r="J24" t="n">
-        <v>114.6</v>
+        <v>111.5</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>120.42</v>
+        <v>117.35</v>
       </c>
       <c r="M24" t="n">
-        <v>122.25</v>
+        <v>119.19</v>
       </c>
       <c r="N24" t="n">
-        <v>120.42</v>
+        <v>117.35</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1625,10 +1625,10 @@
         <v>23</v>
       </c>
       <c r="F25" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H25" t="n">
         <v>115</v>
@@ -1643,19 +1643,19 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>125.42</v>
+        <v>124.94</v>
       </c>
       <c r="M25" t="n">
-        <v>127.25</v>
+        <v>126.27</v>
       </c>
       <c r="N25" t="n">
-        <v>125.42</v>
+        <v>124.94</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1673,37 +1673,37 @@
         <v>24</v>
       </c>
       <c r="F26" t="n">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>120</v>
       </c>
       <c r="I26" t="n">
-        <v>124.6</v>
+        <v>121.5</v>
       </c>
       <c r="J26" t="n">
-        <v>127.25</v>
+        <v>121.5</v>
       </c>
       <c r="K26" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>133.7599999999948</v>
+        <v>127.81</v>
       </c>
       <c r="M26" t="n">
-        <v>136.2799999999948</v>
+        <v>130.13</v>
       </c>
       <c r="N26" t="n">
-        <v>133.7599999999948</v>
+        <v>127.81</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1721,37 +1721,37 @@
         <v>25</v>
       </c>
       <c r="F27" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H27" t="n">
         <v>125</v>
       </c>
       <c r="I27" t="n">
-        <v>126.5</v>
+        <v>129.6</v>
       </c>
       <c r="J27" t="n">
-        <v>126.5</v>
+        <v>129.6</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>132.32</v>
+        <v>135.42</v>
       </c>
       <c r="M27" t="n">
-        <v>134.15</v>
+        <v>137.25</v>
       </c>
       <c r="N27" t="n">
-        <v>132.32</v>
+        <v>135.42</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1769,37 +1769,37 @@
         <v>26</v>
       </c>
       <c r="F28" t="n">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="G28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H28" t="n">
         <v>130</v>
       </c>
       <c r="I28" t="n">
-        <v>133.05</v>
+        <v>134.6</v>
       </c>
       <c r="J28" t="n">
-        <v>133.05</v>
+        <v>137.25</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="L28" t="n">
-        <v>139.23</v>
+        <v>142.5899999999942</v>
       </c>
       <c r="M28" t="n">
-        <v>141.41</v>
+        <v>143.9199999999942</v>
       </c>
       <c r="N28" t="n">
-        <v>139.23</v>
+        <v>142.5899999999942</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1817,7 +1817,7 @@
         <v>27</v>
       </c>
       <c r="F29" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1835,19 +1835,19 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>142.32</v>
+        <v>143.01</v>
       </c>
       <c r="M29" t="n">
-        <v>144.15</v>
+        <v>145.53</v>
       </c>
       <c r="N29" t="n">
-        <v>142.32</v>
+        <v>143.01</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1865,37 +1865,37 @@
         <v>28</v>
       </c>
       <c r="F30" t="n">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H30" t="n">
         <v>140</v>
       </c>
       <c r="I30" t="n">
-        <v>143.05</v>
+        <v>141.5</v>
       </c>
       <c r="J30" t="n">
-        <v>143.05</v>
+        <v>141.5</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>148.39</v>
+        <v>147.32</v>
       </c>
       <c r="M30" t="n">
-        <v>149.72</v>
+        <v>149.15</v>
       </c>
       <c r="N30" t="n">
-        <v>148.39</v>
+        <v>147.32</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1913,37 +1913,37 @@
         <v>29</v>
       </c>
       <c r="F31" t="n">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H31" t="n">
         <v>145</v>
       </c>
       <c r="I31" t="n">
-        <v>149.6</v>
+        <v>148.05</v>
       </c>
       <c r="J31" t="n">
-        <v>149.6</v>
+        <v>148.05</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>155.78</v>
+        <v>154.36</v>
       </c>
       <c r="M31" t="n">
-        <v>157.96</v>
+        <v>156.68</v>
       </c>
       <c r="N31" t="n">
-        <v>164.1399999999939</v>
+        <v>162.9899999999948</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1961,37 +1961,37 @@
         <v>30</v>
       </c>
       <c r="F32" t="n">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="G32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H32" t="n">
         <v>150</v>
       </c>
       <c r="I32" t="n">
-        <v>154.6</v>
+        <v>153.05</v>
       </c>
       <c r="J32" t="n">
-        <v>157.9599999999939</v>
+        <v>156.6799999999948</v>
       </c>
       <c r="K32" t="n">
-        <v>3.359999999993903</v>
+        <v>3.629999999994766</v>
       </c>
       <c r="L32" t="n">
-        <v>164.1399999999939</v>
+        <v>162.9899999999948</v>
       </c>
       <c r="M32" t="n">
-        <v>166.3199999999939</v>
+        <v>165.3099999999948</v>
       </c>
       <c r="N32" t="n">
-        <v>164.1399999999939</v>
+        <v>162.9899999999948</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -2039,7 +2039,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -2057,37 +2057,37 @@
         <v>32</v>
       </c>
       <c r="F34" t="n">
-        <v>13</v>
+        <v>83</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H34" t="n">
         <v>160</v>
       </c>
       <c r="I34" t="n">
-        <v>161.5</v>
+        <v>164.6</v>
       </c>
       <c r="J34" t="n">
-        <v>161.5</v>
+        <v>164.6</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>167.81</v>
+        <v>170.78</v>
       </c>
       <c r="M34" t="n">
-        <v>170.13</v>
+        <v>172.96</v>
       </c>
       <c r="N34" t="n">
-        <v>176.4399999999948</v>
+        <v>179.1399999999939</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2105,37 +2105,37 @@
         <v>33</v>
       </c>
       <c r="F35" t="n">
-        <v>13</v>
+        <v>83</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H35" t="n">
         <v>165</v>
       </c>
       <c r="I35" t="n">
-        <v>166.5</v>
+        <v>169.6</v>
       </c>
       <c r="J35" t="n">
-        <v>170.1299999999948</v>
+        <v>172.9599999999939</v>
       </c>
       <c r="K35" t="n">
-        <v>3.629999999994766</v>
+        <v>3.359999999993903</v>
       </c>
       <c r="L35" t="n">
-        <v>176.4399999999948</v>
+        <v>179.1399999999939</v>
       </c>
       <c r="M35" t="n">
-        <v>178.7599999999948</v>
+        <v>181.3199999999939</v>
       </c>
       <c r="N35" t="n">
-        <v>176.4399999999948</v>
+        <v>179.1399999999939</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -2153,10 +2153,10 @@
         <v>34</v>
       </c>
       <c r="F36" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
         <v>170</v>
@@ -2171,19 +2171,19 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>177.35</v>
+        <v>177.01</v>
       </c>
       <c r="M36" t="n">
-        <v>179.19</v>
+        <v>178.53</v>
       </c>
       <c r="N36" t="n">
-        <v>185.0399999999901</v>
+        <v>184.0399999999904</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2201,10 +2201,10 @@
         <v>35</v>
       </c>
       <c r="F37" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
         <v>175</v>
@@ -2213,25 +2213,25 @@
         <v>176.5</v>
       </c>
       <c r="J37" t="n">
-        <v>179.1899999999901</v>
+        <v>178.5299999999904</v>
       </c>
       <c r="K37" t="n">
-        <v>2.689999999990107</v>
+        <v>2.029999999990395</v>
       </c>
       <c r="L37" t="n">
-        <v>185.0399999999901</v>
+        <v>184.0399999999904</v>
       </c>
       <c r="M37" t="n">
-        <v>186.8799999999901</v>
+        <v>185.5599999999904</v>
       </c>
       <c r="N37" t="n">
-        <v>185.0399999999901</v>
+        <v>184.0399999999904</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -2249,7 +2249,7 @@
         <v>36</v>
       </c>
       <c r="F38" t="n">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G38" t="n">
         <v>5</v>
@@ -2267,19 +2267,19 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>191.11</v>
+        <v>190.42</v>
       </c>
       <c r="M38" t="n">
-        <v>193.63</v>
+        <v>192.25</v>
       </c>
       <c r="N38" t="n">
-        <v>191.11</v>
+        <v>190.42</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2297,37 +2297,37 @@
         <v>37</v>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H39" t="n">
         <v>185</v>
       </c>
       <c r="I39" t="n">
-        <v>186.5</v>
+        <v>189.6</v>
       </c>
       <c r="J39" t="n">
-        <v>186.5</v>
+        <v>192.25</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="L39" t="n">
-        <v>192.01</v>
+        <v>198.559999999997</v>
       </c>
       <c r="M39" t="n">
-        <v>193.53</v>
+        <v>200.879999999997</v>
       </c>
       <c r="N39" t="n">
-        <v>192.01</v>
+        <v>198.559999999997</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -2345,37 +2345,37 @@
         <v>38</v>
       </c>
       <c r="F40" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H40" t="n">
         <v>190</v>
       </c>
       <c r="I40" t="n">
-        <v>191.5</v>
+        <v>194.6</v>
       </c>
       <c r="J40" t="n">
-        <v>193.5299999999922</v>
+        <v>194.6</v>
       </c>
       <c r="K40" t="n">
-        <v>2.029999999992214</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>200.0399999999922</v>
+        <v>200.78</v>
       </c>
       <c r="M40" t="n">
-        <v>202.5599999999922</v>
+        <v>202.96</v>
       </c>
       <c r="N40" t="n">
-        <v>200.0399999999922</v>
+        <v>200.78</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2393,7 +2393,7 @@
         <v>39</v>
       </c>
       <c r="F41" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="G41" t="n">
         <v>1</v>
@@ -2411,19 +2411,19 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>204.56</v>
+        <v>203.56</v>
       </c>
       <c r="M41" t="n">
-        <v>207.08</v>
+        <v>205.08</v>
       </c>
       <c r="N41" t="n">
-        <v>204.56</v>
+        <v>203.56</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -2441,37 +2441,37 @@
         <v>40</v>
       </c>
       <c r="F42" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H42" t="n">
         <v>200</v>
       </c>
       <c r="I42" t="n">
-        <v>203.05</v>
+        <v>204.6</v>
       </c>
       <c r="J42" t="n">
-        <v>203.05</v>
+        <v>204.6</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>209.56</v>
+        <v>210.45</v>
       </c>
       <c r="M42" t="n">
-        <v>212.08</v>
+        <v>212.29</v>
       </c>
       <c r="N42" t="n">
-        <v>209.56</v>
+        <v>210.45</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2489,37 +2489,37 @@
         <v>41</v>
       </c>
       <c r="F43" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="G43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H43" t="n">
         <v>205</v>
       </c>
       <c r="I43" t="n">
-        <v>206.5</v>
+        <v>208.05</v>
       </c>
       <c r="J43" t="n">
-        <v>206.5</v>
+        <v>208.05</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>213.01</v>
+        <v>214.23</v>
       </c>
       <c r="M43" t="n">
-        <v>215.53</v>
+        <v>216.41</v>
       </c>
       <c r="N43" t="n">
-        <v>213.01</v>
+        <v>214.23</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -2537,10 +2537,10 @@
         <v>42</v>
       </c>
       <c r="F44" t="n">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="G44" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H44" t="n">
         <v>210</v>
@@ -2555,19 +2555,19 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>218.87</v>
+        <v>219.56</v>
       </c>
       <c r="M44" t="n">
-        <v>220.7</v>
+        <v>222.08</v>
       </c>
       <c r="N44" t="n">
-        <v>218.87</v>
+        <v>219.56</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2585,37 +2585,37 @@
         <v>43</v>
       </c>
       <c r="F45" t="n">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="G45" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H45" t="n">
         <v>215</v>
       </c>
       <c r="I45" t="n">
-        <v>219.6</v>
+        <v>218.05</v>
       </c>
       <c r="J45" t="n">
-        <v>219.6</v>
+        <v>218.05</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>225.45</v>
+        <v>223.56</v>
       </c>
       <c r="M45" t="n">
-        <v>227.29</v>
+        <v>225.08</v>
       </c>
       <c r="N45" t="n">
-        <v>225.45</v>
+        <v>223.56</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -2633,37 +2633,37 @@
         <v>44</v>
       </c>
       <c r="F46" t="n">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="G46" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H46" t="n">
         <v>220</v>
       </c>
       <c r="I46" t="n">
-        <v>224.6</v>
+        <v>223.05</v>
       </c>
       <c r="J46" t="n">
-        <v>224.6</v>
+        <v>225.0799999999922</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>2.029999999992214</v>
       </c>
       <c r="L46" t="n">
-        <v>230.91</v>
+        <v>231.5899999999922</v>
       </c>
       <c r="M46" t="n">
-        <v>233.23</v>
+        <v>234.1099999999922</v>
       </c>
       <c r="N46" t="n">
-        <v>230.91</v>
+        <v>231.5899999999922</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2681,37 +2681,37 @@
         <v>45</v>
       </c>
       <c r="F47" t="n">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="G47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H47" t="n">
         <v>225</v>
       </c>
       <c r="I47" t="n">
-        <v>226.5</v>
+        <v>228.05</v>
       </c>
       <c r="J47" t="n">
-        <v>226.5</v>
+        <v>234.1099999999859</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>6.059999999985905</v>
       </c>
       <c r="L47" t="n">
-        <v>232.32</v>
+        <v>240.4199999999859</v>
       </c>
       <c r="M47" t="n">
-        <v>234.15</v>
+        <v>242.7399999999859</v>
       </c>
       <c r="N47" t="n">
-        <v>232.32</v>
+        <v>240.4199999999859</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -2729,37 +2729,37 @@
         <v>46</v>
       </c>
       <c r="F48" t="n">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="G48" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H48" t="n">
         <v>230</v>
       </c>
       <c r="I48" t="n">
-        <v>234.6</v>
+        <v>233.05</v>
       </c>
       <c r="J48" t="n">
-        <v>234.6</v>
+        <v>233.05</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>240.91</v>
+        <v>239.56</v>
       </c>
       <c r="M48" t="n">
-        <v>243.23</v>
+        <v>242.08</v>
       </c>
       <c r="N48" t="n">
-        <v>240.91</v>
+        <v>239.56</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2777,10 +2777,10 @@
         <v>47</v>
       </c>
       <c r="F49" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="G49" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
         <v>235</v>
@@ -2795,19 +2795,19 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>241.84</v>
+        <v>242.81</v>
       </c>
       <c r="M49" t="n">
-        <v>243.17</v>
+        <v>245.13</v>
       </c>
       <c r="N49" t="n">
-        <v>241.84</v>
+        <v>242.81</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -2825,37 +2825,37 @@
         <v>48</v>
       </c>
       <c r="F50" t="n">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="G50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H50" t="n">
         <v>240</v>
       </c>
       <c r="I50" t="n">
-        <v>244.6</v>
+        <v>241.5</v>
       </c>
       <c r="J50" t="n">
-        <v>244.6</v>
+        <v>241.5</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>250.45</v>
+        <v>247.32</v>
       </c>
       <c r="M50" t="n">
-        <v>252.29</v>
+        <v>249.15</v>
       </c>
       <c r="N50" t="n">
-        <v>250.45</v>
+        <v>247.32</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2873,10 +2873,10 @@
         <v>49</v>
       </c>
       <c r="F51" t="n">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="G51" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H51" t="n">
         <v>245</v>
@@ -2891,19 +2891,19 @@
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>253.56</v>
+        <v>253.9</v>
       </c>
       <c r="M51" t="n">
-        <v>255.08</v>
+        <v>255.74</v>
       </c>
       <c r="N51" t="n">
-        <v>253.56</v>
+        <v>253.9</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -2921,10 +2921,10 @@
         <v>50</v>
       </c>
       <c r="F52" t="n">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="G52" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H52" t="n">
         <v>250</v>
@@ -2939,19 +2939,19 @@
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>259.23</v>
+        <v>258.87</v>
       </c>
       <c r="M52" t="n">
-        <v>261.41</v>
+        <v>260.7</v>
       </c>
       <c r="N52" t="n">
-        <v>267.5899999999933</v>
+        <v>266.5199999999942</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2969,10 +2969,10 @@
         <v>51</v>
       </c>
       <c r="F53" t="n">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H53" t="n">
         <v>255</v>
@@ -2981,25 +2981,25 @@
         <v>258.05</v>
       </c>
       <c r="J53" t="n">
-        <v>261.4099999999933</v>
+        <v>260.7</v>
       </c>
       <c r="K53" t="n">
-        <v>3.359999999993306</v>
+        <v>2.65</v>
       </c>
       <c r="L53" t="n">
-        <v>267.5899999999933</v>
+        <v>266.5199999999942</v>
       </c>
       <c r="M53" t="n">
-        <v>269.7699999999933</v>
+        <v>268.35</v>
       </c>
       <c r="N53" t="n">
-        <v>267.5899999999933</v>
+        <v>266.5199999999942</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -3017,37 +3017,37 @@
         <v>52</v>
       </c>
       <c r="F54" t="n">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H54" t="n">
         <v>260</v>
       </c>
       <c r="I54" t="n">
-        <v>263.05</v>
+        <v>264.6</v>
       </c>
       <c r="J54" t="n">
-        <v>269.7699999999884</v>
+        <v>264.6</v>
       </c>
       <c r="K54" t="n">
-        <v>6.719999999988374</v>
+        <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>276.0799999999884</v>
+        <v>270.78</v>
       </c>
       <c r="M54" t="n">
-        <v>278.4</v>
+        <v>272.96</v>
       </c>
       <c r="N54" t="n">
-        <v>276.0799999999884</v>
+        <v>270.78</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -3065,37 +3065,37 @@
         <v>53</v>
       </c>
       <c r="F55" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
         <v>265</v>
       </c>
       <c r="I55" t="n">
-        <v>269.6</v>
+        <v>266.5</v>
       </c>
       <c r="J55" t="n">
-        <v>269.6</v>
+        <v>266.5</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>275.11</v>
+        <v>271.84</v>
       </c>
       <c r="M55" t="n">
-        <v>276.63</v>
+        <v>273.17</v>
       </c>
       <c r="N55" t="n">
-        <v>275.11</v>
+        <v>271.84</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -3113,10 +3113,10 @@
         <v>54</v>
       </c>
       <c r="F56" t="n">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="G56" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H56" t="n">
         <v>270</v>
@@ -3131,19 +3131,19 @@
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>280.42</v>
+        <v>281.11</v>
       </c>
       <c r="M56" t="n">
-        <v>282.25</v>
+        <v>283.63</v>
       </c>
       <c r="N56" t="n">
-        <v>280.42</v>
+        <v>281.11</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -3161,7 +3161,7 @@
         <v>55</v>
       </c>
       <c r="F57" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -3179,19 +3179,19 @@
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>282.81</v>
+        <v>282.32</v>
       </c>
       <c r="M57" t="n">
-        <v>285.13</v>
+        <v>284.15</v>
       </c>
       <c r="N57" t="n">
-        <v>282.81</v>
+        <v>282.32</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -3209,37 +3209,37 @@
         <v>56</v>
       </c>
       <c r="F58" t="n">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="G58" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H58" t="n">
         <v>280</v>
       </c>
       <c r="I58" t="n">
-        <v>283.05</v>
+        <v>284.6</v>
       </c>
       <c r="J58" t="n">
-        <v>283.05</v>
+        <v>284.6</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>288.9</v>
+        <v>290.42</v>
       </c>
       <c r="M58" t="n">
-        <v>290.74</v>
+        <v>292.25</v>
       </c>
       <c r="N58" t="n">
-        <v>288.9</v>
+        <v>290.42</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3257,10 +3257,10 @@
         <v>57</v>
       </c>
       <c r="F59" t="n">
-        <v>84</v>
+        <v>32</v>
       </c>
       <c r="G59" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H59" t="n">
         <v>285</v>
@@ -3275,19 +3275,19 @@
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>296.11</v>
+        <v>295.45</v>
       </c>
       <c r="M59" t="n">
-        <v>298.63</v>
+        <v>297.29</v>
       </c>
       <c r="N59" t="n">
-        <v>296.11</v>
+        <v>295.45</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -3305,37 +3305,37 @@
         <v>58</v>
       </c>
       <c r="F60" t="n">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="G60" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H60" t="n">
         <v>290</v>
       </c>
       <c r="I60" t="n">
-        <v>293.05</v>
+        <v>294.6</v>
       </c>
       <c r="J60" t="n">
-        <v>293.05</v>
+        <v>297.2899999999951</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>2.689999999995052</v>
       </c>
       <c r="L60" t="n">
-        <v>298.9</v>
+        <v>303.6</v>
       </c>
       <c r="M60" t="n">
-        <v>300.74</v>
+        <v>305.9199999999951</v>
       </c>
       <c r="N60" t="n">
-        <v>298.9</v>
+        <v>303.6</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3353,37 +3353,37 @@
         <v>59</v>
       </c>
       <c r="F61" t="n">
-        <v>88</v>
+        <v>10</v>
       </c>
       <c r="G61" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
         <v>295</v>
       </c>
       <c r="I61" t="n">
-        <v>299.6</v>
+        <v>296.5</v>
       </c>
       <c r="J61" t="n">
-        <v>299.6</v>
+        <v>296.5</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>305.91</v>
+        <v>302.81</v>
       </c>
       <c r="M61" t="n">
-        <v>308.23</v>
+        <v>305.13</v>
       </c>
       <c r="N61" t="n">
-        <v>305.91</v>
+        <v>302.81</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -3401,37 +3401,37 @@
         <v>60</v>
       </c>
       <c r="F62" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H62" t="n">
         <v>300</v>
       </c>
       <c r="I62" t="n">
-        <v>301.5</v>
+        <v>303.05</v>
       </c>
       <c r="J62" t="n">
-        <v>301.5</v>
+        <v>303.05</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>307.35</v>
+        <v>309.36</v>
       </c>
       <c r="M62" t="n">
-        <v>309.19</v>
+        <v>311.68</v>
       </c>
       <c r="N62" t="n">
-        <v>307.35</v>
+        <v>309.36</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3449,10 +3449,10 @@
         <v>61</v>
       </c>
       <c r="F63" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="G63" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
         <v>305</v>
@@ -3467,19 +3467,19 @@
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>312.35</v>
+        <v>313.01</v>
       </c>
       <c r="M63" t="n">
-        <v>314.19</v>
+        <v>315.53</v>
       </c>
       <c r="N63" t="n">
-        <v>312.35</v>
+        <v>313.01</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -3497,37 +3497,37 @@
         <v>62</v>
       </c>
       <c r="F64" t="n">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="G64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H64" t="n">
         <v>310</v>
       </c>
       <c r="I64" t="n">
-        <v>314.6</v>
+        <v>311.5</v>
       </c>
       <c r="J64" t="n">
-        <v>314.6</v>
+        <v>311.5</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>320.91</v>
+        <v>317.81</v>
       </c>
       <c r="M64" t="n">
-        <v>323.23</v>
+        <v>320.13</v>
       </c>
       <c r="N64" t="n">
-        <v>320.91</v>
+        <v>317.81</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3545,37 +3545,37 @@
         <v>63</v>
       </c>
       <c r="F65" t="n">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="G65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
         <v>315</v>
       </c>
       <c r="I65" t="n">
-        <v>319.6</v>
+        <v>316.5</v>
       </c>
       <c r="J65" t="n">
-        <v>323.2299999999974</v>
+        <v>316.5</v>
       </c>
       <c r="K65" t="n">
-        <v>3.629999999997381</v>
+        <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>329.5399999999974</v>
+        <v>322.81</v>
       </c>
       <c r="M65" t="n">
-        <v>331.8599999999974</v>
+        <v>325.13</v>
       </c>
       <c r="N65" t="n">
-        <v>329.5399999999974</v>
+        <v>322.81</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -3593,37 +3593,37 @@
         <v>64</v>
       </c>
       <c r="F66" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H66" t="n">
         <v>320</v>
       </c>
       <c r="I66" t="n">
-        <v>321.5</v>
+        <v>323.05</v>
       </c>
       <c r="J66" t="n">
-        <v>321.5</v>
+        <v>323.05</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>327.68</v>
+        <v>328.9</v>
       </c>
       <c r="M66" t="n">
-        <v>329.86</v>
+        <v>330.74</v>
       </c>
       <c r="N66" t="n">
-        <v>327.68</v>
+        <v>328.9</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3641,7 +3641,7 @@
         <v>65</v>
       </c>
       <c r="F67" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G67" t="n">
         <v>1</v>
@@ -3653,25 +3653,25 @@
         <v>328.05</v>
       </c>
       <c r="J67" t="n">
-        <v>328.05</v>
+        <v>330.7399999999951</v>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>2.689999999995052</v>
       </c>
       <c r="L67" t="n">
-        <v>333.87</v>
+        <v>337.05</v>
       </c>
       <c r="M67" t="n">
-        <v>335.7</v>
+        <v>339.3699999999951</v>
       </c>
       <c r="N67" t="n">
-        <v>333.87</v>
+        <v>337.05</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -3689,7 +3689,7 @@
         <v>66</v>
       </c>
       <c r="F68" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="G68" t="n">
         <v>4</v>
@@ -3707,19 +3707,19 @@
         <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>339.56</v>
+        <v>339.23</v>
       </c>
       <c r="M68" t="n">
-        <v>342.08</v>
+        <v>341.41</v>
       </c>
       <c r="N68" t="n">
-        <v>339.56</v>
+        <v>339.23</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3737,7 +3737,7 @@
         <v>67</v>
       </c>
       <c r="F69" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="G69" t="n">
         <v>3</v>
@@ -3755,19 +3755,19 @@
         <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>342.81</v>
+        <v>343.01</v>
       </c>
       <c r="M69" t="n">
-        <v>345.13</v>
+        <v>345.53</v>
       </c>
       <c r="N69" t="n">
-        <v>342.81</v>
+        <v>343.01</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -3785,37 +3785,37 @@
         <v>68</v>
       </c>
       <c r="F70" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="G70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
         <v>340</v>
       </c>
       <c r="I70" t="n">
-        <v>344.6</v>
+        <v>341.5</v>
       </c>
       <c r="J70" t="n">
-        <v>344.6</v>
+        <v>341.5</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>350.78</v>
+        <v>347.32</v>
       </c>
       <c r="M70" t="n">
-        <v>352.96</v>
+        <v>349.15</v>
       </c>
       <c r="N70" t="n">
-        <v>350.78</v>
+        <v>347.32</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3833,37 +3833,37 @@
         <v>69</v>
       </c>
       <c r="F71" t="n">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="G71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H71" t="n">
         <v>345</v>
       </c>
       <c r="I71" t="n">
-        <v>346.5</v>
+        <v>349.6</v>
       </c>
       <c r="J71" t="n">
-        <v>346.5</v>
+        <v>349.6</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>352.81</v>
+        <v>356.11</v>
       </c>
       <c r="M71" t="n">
-        <v>355.13</v>
+        <v>358.63</v>
       </c>
       <c r="N71" t="n">
-        <v>352.81</v>
+        <v>356.11</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -3881,37 +3881,37 @@
         <v>70</v>
       </c>
       <c r="F72" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="G72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H72" t="n">
         <v>350</v>
       </c>
       <c r="I72" t="n">
-        <v>354.6</v>
+        <v>351.5</v>
       </c>
       <c r="J72" t="n">
-        <v>354.6</v>
+        <v>351.5</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>360.11</v>
+        <v>357.35</v>
       </c>
       <c r="M72" t="n">
-        <v>361.63</v>
+        <v>359.19</v>
       </c>
       <c r="N72" t="n">
-        <v>360.11</v>
+        <v>357.35</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3929,10 +3929,10 @@
         <v>71</v>
       </c>
       <c r="F73" t="n">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="G73" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H73" t="n">
         <v>355</v>
@@ -3959,7 +3959,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -3977,10 +3977,10 @@
         <v>72</v>
       </c>
       <c r="F74" t="n">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H74" t="n">
         <v>360</v>
@@ -3995,19 +3995,19 @@
         <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>367.68</v>
+        <v>367.35</v>
       </c>
       <c r="M74" t="n">
-        <v>369.86</v>
+        <v>369.19</v>
       </c>
       <c r="N74" t="n">
-        <v>367.68</v>
+        <v>367.35</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -4025,37 +4025,37 @@
         <v>73</v>
       </c>
       <c r="F75" t="n">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="G75" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H75" t="n">
         <v>365</v>
       </c>
       <c r="I75" t="n">
-        <v>366.5</v>
+        <v>368.05</v>
       </c>
       <c r="J75" t="n">
-        <v>366.5</v>
+        <v>368.05</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>373.01</v>
+        <v>374.36</v>
       </c>
       <c r="M75" t="n">
-        <v>375.53</v>
+        <v>376.68</v>
       </c>
       <c r="N75" t="n">
-        <v>373.01</v>
+        <v>374.36</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -4073,10 +4073,10 @@
         <v>74</v>
       </c>
       <c r="F76" t="n">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="G76" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H76" t="n">
         <v>370</v>
@@ -4091,19 +4091,19 @@
         <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>380.42</v>
+        <v>380.11</v>
       </c>
       <c r="M76" t="n">
-        <v>382.25</v>
+        <v>381.63</v>
       </c>
       <c r="N76" t="n">
-        <v>380.42</v>
+        <v>380.11</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -4121,10 +4121,10 @@
         <v>75</v>
       </c>
       <c r="F77" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="G77" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H77" t="n">
         <v>375</v>
@@ -4139,19 +4139,19 @@
         <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>384.56</v>
+        <v>383.39</v>
       </c>
       <c r="M77" t="n">
-        <v>387.08</v>
+        <v>384.72</v>
       </c>
       <c r="N77" t="n">
-        <v>384.56</v>
+        <v>383.39</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -4169,37 +4169,37 @@
         <v>76</v>
       </c>
       <c r="F78" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="G78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H78" t="n">
         <v>380</v>
       </c>
       <c r="I78" t="n">
-        <v>384.6</v>
+        <v>383.05</v>
       </c>
       <c r="J78" t="n">
-        <v>384.6</v>
+        <v>383.05</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>391.11</v>
+        <v>389.23</v>
       </c>
       <c r="M78" t="n">
-        <v>393.63</v>
+        <v>391.41</v>
       </c>
       <c r="N78" t="n">
-        <v>391.11</v>
+        <v>389.23</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -4217,10 +4217,10 @@
         <v>77</v>
       </c>
       <c r="F79" t="n">
-        <v>41</v>
+        <v>86</v>
       </c>
       <c r="G79" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H79" t="n">
         <v>385</v>
@@ -4229,25 +4229,25 @@
         <v>389.6</v>
       </c>
       <c r="J79" t="n">
-        <v>393.6299999999952</v>
+        <v>389.6</v>
       </c>
       <c r="K79" t="n">
-        <v>4.029999999995198</v>
+        <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>399.9399999999952</v>
+        <v>395.91</v>
       </c>
       <c r="M79" t="n">
-        <v>402.2599999999952</v>
+        <v>398.23</v>
       </c>
       <c r="N79" t="n">
-        <v>399.9399999999952</v>
+        <v>395.91</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -4265,37 +4265,37 @@
         <v>78</v>
       </c>
       <c r="F80" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H80" t="n">
         <v>390</v>
       </c>
       <c r="I80" t="n">
-        <v>394.6</v>
+        <v>393.05</v>
       </c>
       <c r="J80" t="n">
-        <v>402.2599999999926</v>
+        <v>393.05</v>
       </c>
       <c r="K80" t="n">
-        <v>7.659999999992579</v>
+        <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>408.5699999999926</v>
+        <v>398.87</v>
       </c>
       <c r="M80" t="n">
-        <v>410.8899999999926</v>
+        <v>400.7</v>
       </c>
       <c r="N80" t="n">
-        <v>408.5699999999926</v>
+        <v>398.87</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4313,37 +4313,37 @@
         <v>79</v>
       </c>
       <c r="F81" t="n">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="G81" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H81" t="n">
         <v>395</v>
       </c>
       <c r="I81" t="n">
-        <v>398.05</v>
+        <v>399.6</v>
       </c>
       <c r="J81" t="n">
-        <v>398.05</v>
+        <v>399.6</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>403.87</v>
+        <v>406.11</v>
       </c>
       <c r="M81" t="n">
-        <v>405.7</v>
+        <v>408.63</v>
       </c>
       <c r="N81" t="n">
-        <v>403.87</v>
+        <v>406.11</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -4361,37 +4361,37 @@
         <v>80</v>
       </c>
       <c r="F82" t="n">
-        <v>12</v>
+        <v>85</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H82" t="n">
         <v>400</v>
       </c>
       <c r="I82" t="n">
-        <v>401.5</v>
+        <v>404.6</v>
       </c>
       <c r="J82" t="n">
-        <v>401.5</v>
+        <v>404.6</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>407.81</v>
+        <v>410.91</v>
       </c>
       <c r="M82" t="n">
-        <v>410.13</v>
+        <v>413.23</v>
       </c>
       <c r="N82" t="n">
-        <v>407.81</v>
+        <v>410.91</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4409,37 +4409,37 @@
         <v>81</v>
       </c>
       <c r="F83" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G83" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H83" t="n">
         <v>405</v>
       </c>
       <c r="I83" t="n">
-        <v>408.05</v>
+        <v>406.5</v>
       </c>
       <c r="J83" t="n">
-        <v>408.05</v>
+        <v>406.5</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>413.39</v>
+        <v>413.01</v>
       </c>
       <c r="M83" t="n">
-        <v>414.72</v>
+        <v>415.53</v>
       </c>
       <c r="N83" t="n">
-        <v>413.39</v>
+        <v>413.01</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -4457,37 +4457,37 @@
         <v>82</v>
       </c>
       <c r="F84" t="n">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="G84" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H84" t="n">
         <v>410</v>
       </c>
       <c r="I84" t="n">
-        <v>413.05</v>
+        <v>414.6</v>
       </c>
       <c r="J84" t="n">
-        <v>414.7199999999946</v>
+        <v>414.6</v>
       </c>
       <c r="K84" t="n">
-        <v>1.669999999994616</v>
+        <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>421.0299999999946</v>
+        <v>420.91</v>
       </c>
       <c r="M84" t="n">
-        <v>423.35</v>
+        <v>423.23</v>
       </c>
       <c r="N84" t="n">
-        <v>421.0299999999946</v>
+        <v>420.91</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4505,37 +4505,37 @@
         <v>83</v>
       </c>
       <c r="F85" t="n">
-        <v>78</v>
+        <v>3</v>
       </c>
       <c r="G85" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H85" t="n">
         <v>415</v>
       </c>
       <c r="I85" t="n">
-        <v>419.6</v>
+        <v>416.5</v>
       </c>
       <c r="J85" t="n">
-        <v>419.6</v>
+        <v>416.5</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>425.78</v>
+        <v>422.68</v>
       </c>
       <c r="M85" t="n">
-        <v>427.96</v>
+        <v>424.86</v>
       </c>
       <c r="N85" t="n">
-        <v>425.78</v>
+        <v>422.68</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -4553,37 +4553,37 @@
         <v>84</v>
       </c>
       <c r="F86" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H86" t="n">
         <v>420</v>
       </c>
       <c r="I86" t="n">
-        <v>421.5</v>
+        <v>424.6</v>
       </c>
       <c r="J86" t="n">
-        <v>421.5</v>
+        <v>424.6</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>428.01</v>
+        <v>430.91</v>
       </c>
       <c r="M86" t="n">
-        <v>430.53</v>
+        <v>433.23</v>
       </c>
       <c r="N86" t="n">
-        <v>428.01</v>
+        <v>430.91</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4601,37 +4601,37 @@
         <v>85</v>
       </c>
       <c r="F87" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="G87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H87" t="n">
         <v>425</v>
       </c>
       <c r="I87" t="n">
-        <v>429.6</v>
+        <v>426.5</v>
       </c>
       <c r="J87" t="n">
-        <v>429.6</v>
+        <v>426.5</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
       </c>
       <c r="L87" t="n">
-        <v>436.11</v>
+        <v>432.68</v>
       </c>
       <c r="M87" t="n">
-        <v>438.63</v>
+        <v>434.86</v>
       </c>
       <c r="N87" t="n">
-        <v>436.11</v>
+        <v>432.68</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -4649,37 +4649,37 @@
         <v>86</v>
       </c>
       <c r="F88" t="n">
-        <v>77</v>
+        <v>21</v>
       </c>
       <c r="G88" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H88" t="n">
         <v>430</v>
       </c>
       <c r="I88" t="n">
-        <v>434.6</v>
+        <v>433.05</v>
       </c>
       <c r="J88" t="n">
-        <v>434.6</v>
+        <v>433.05</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>440.45</v>
+        <v>438.87</v>
       </c>
       <c r="M88" t="n">
-        <v>442.29</v>
+        <v>440.7</v>
       </c>
       <c r="N88" t="n">
-        <v>440.45</v>
+        <v>438.87</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4697,10 +4697,10 @@
         <v>87</v>
       </c>
       <c r="F89" t="n">
-        <v>64</v>
+        <v>18</v>
       </c>
       <c r="G89" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H89" t="n">
         <v>435</v>
@@ -4709,25 +4709,25 @@
         <v>438.05</v>
       </c>
       <c r="J89" t="n">
-        <v>438.05</v>
+        <v>440.7</v>
       </c>
       <c r="K89" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="L89" t="n">
-        <v>444.56</v>
+        <v>446.8799999999978</v>
       </c>
       <c r="M89" t="n">
-        <v>447.08</v>
+        <v>449.0599999999978</v>
       </c>
       <c r="N89" t="n">
-        <v>444.56</v>
+        <v>446.8799999999978</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -4745,37 +4745,37 @@
         <v>88</v>
       </c>
       <c r="F90" t="n">
-        <v>71</v>
+        <v>4</v>
       </c>
       <c r="G90" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H90" t="n">
         <v>440</v>
       </c>
       <c r="I90" t="n">
-        <v>443.05</v>
+        <v>441.5</v>
       </c>
       <c r="J90" t="n">
-        <v>447.0799999999952</v>
+        <v>441.5</v>
       </c>
       <c r="K90" t="n">
-        <v>4.029999999995198</v>
+        <v>0</v>
       </c>
       <c r="L90" t="n">
-        <v>453.3899999999952</v>
+        <v>448.01</v>
       </c>
       <c r="M90" t="n">
-        <v>455.7099999999952</v>
+        <v>450.53</v>
       </c>
       <c r="N90" t="n">
-        <v>497.9899999999974</v>
+        <v>497.0399999999952</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4793,37 +4793,37 @@
         <v>89</v>
       </c>
       <c r="F91" t="n">
+        <v>44</v>
+      </c>
+      <c r="G91" t="n">
         <v>2</v>
-      </c>
-      <c r="G91" t="n">
-        <v>0</v>
       </c>
       <c r="H91" t="n">
         <v>445</v>
       </c>
       <c r="I91" t="n">
-        <v>446.5</v>
+        <v>449.6</v>
       </c>
       <c r="J91" t="n">
-        <v>446.5</v>
+        <v>449.6</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>452.35</v>
+        <v>456.11</v>
       </c>
       <c r="M91" t="n">
-        <v>454.19</v>
+        <v>458.63</v>
       </c>
       <c r="N91" t="n">
-        <v>497.35</v>
+        <v>501.11</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -4841,37 +4841,37 @@
         <v>90</v>
       </c>
       <c r="F92" t="n">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="G92" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H92" t="n">
         <v>450</v>
       </c>
       <c r="I92" t="n">
-        <v>451.5</v>
+        <v>453.05</v>
       </c>
       <c r="J92" t="n">
-        <v>451.5</v>
+        <v>453.05</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
       </c>
       <c r="L92" t="n">
-        <v>458.01</v>
+        <v>458.87</v>
       </c>
       <c r="M92" t="n">
-        <v>460.53</v>
+        <v>460.7</v>
       </c>
       <c r="N92" t="n">
-        <v>529.3</v>
+        <v>524.2099999999928</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4889,37 +4889,37 @@
         <v>91</v>
       </c>
       <c r="F93" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H93" t="n">
         <v>455</v>
       </c>
       <c r="I93" t="n">
-        <v>459.6</v>
+        <v>458.05</v>
       </c>
       <c r="J93" t="n">
-        <v>459.6</v>
+        <v>458.05</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>464.94</v>
+        <v>464.56</v>
       </c>
       <c r="M93" t="n">
-        <v>466.27</v>
+        <v>467.08</v>
       </c>
       <c r="N93" t="n">
-        <v>464.94</v>
+        <v>464.56</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -4937,7 +4937,7 @@
         <v>92</v>
       </c>
       <c r="F94" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G94" t="n">
         <v>3</v>
@@ -4967,7 +4967,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4985,37 +4985,37 @@
         <v>93</v>
       </c>
       <c r="F95" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="G95" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H95" t="n">
         <v>465</v>
       </c>
       <c r="I95" t="n">
-        <v>466.5</v>
+        <v>468.05</v>
       </c>
       <c r="J95" t="n">
-        <v>470.1299999999974</v>
+        <v>468.05</v>
       </c>
       <c r="K95" t="n">
-        <v>3.629999999997381</v>
+        <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>476.4399999999974</v>
+        <v>473.9</v>
       </c>
       <c r="M95" t="n">
-        <v>478.7599999999974</v>
+        <v>475.74</v>
       </c>
       <c r="N95" t="n">
-        <v>511.4399999999974</v>
+        <v>508.9</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -5033,37 +5033,37 @@
         <v>94</v>
       </c>
       <c r="F96" t="n">
-        <v>71</v>
+        <v>4</v>
       </c>
       <c r="G96" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H96" t="n">
         <v>470</v>
       </c>
       <c r="I96" t="n">
-        <v>473.05</v>
+        <v>471.5</v>
       </c>
       <c r="J96" t="n">
-        <v>473.05</v>
+        <v>471.5</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>479.36</v>
+        <v>478.01</v>
       </c>
       <c r="M96" t="n">
-        <v>481.68</v>
+        <v>480.53</v>
       </c>
       <c r="N96" t="n">
-        <v>497.9899999999974</v>
+        <v>497.0399999999952</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -5081,37 +5081,37 @@
         <v>95</v>
       </c>
       <c r="F97" t="n">
+        <v>44</v>
+      </c>
+      <c r="G97" t="n">
         <v>2</v>
-      </c>
-      <c r="G97" t="n">
-        <v>0</v>
       </c>
       <c r="H97" t="n">
         <v>475</v>
       </c>
       <c r="I97" t="n">
-        <v>476.5</v>
+        <v>479.6</v>
       </c>
       <c r="J97" t="n">
-        <v>476.5</v>
+        <v>479.6</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
       </c>
       <c r="L97" t="n">
-        <v>482.35</v>
+        <v>486.11</v>
       </c>
       <c r="M97" t="n">
-        <v>484.19</v>
+        <v>488.63</v>
       </c>
       <c r="N97" t="n">
-        <v>497.35</v>
+        <v>501.11</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -5129,37 +5129,37 @@
         <v>96</v>
       </c>
       <c r="F98" t="n">
-        <v>71</v>
+        <v>4</v>
       </c>
       <c r="G98" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H98" t="n">
         <v>480</v>
       </c>
       <c r="I98" t="n">
-        <v>483.05</v>
+        <v>481.5</v>
       </c>
       <c r="J98" t="n">
-        <v>483.05</v>
+        <v>481.5</v>
       </c>
       <c r="K98" t="n">
         <v>0</v>
       </c>
       <c r="L98" t="n">
-        <v>489.36</v>
+        <v>488.01</v>
       </c>
       <c r="M98" t="n">
-        <v>491.68</v>
+        <v>490.53</v>
       </c>
       <c r="N98" t="n">
-        <v>497.9899999999974</v>
+        <v>497.0399999999952</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -5177,37 +5177,37 @@
         <v>97</v>
       </c>
       <c r="F99" t="n">
-        <v>71</v>
+        <v>4</v>
       </c>
       <c r="G99" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H99" t="n">
         <v>485</v>
       </c>
       <c r="I99" t="n">
-        <v>488.05</v>
+        <v>486.5</v>
       </c>
       <c r="J99" t="n">
-        <v>491.6799999999974</v>
+        <v>490.5299999999952</v>
       </c>
       <c r="K99" t="n">
-        <v>3.629999999997381</v>
+        <v>4.029999999995198</v>
       </c>
       <c r="L99" t="n">
-        <v>497.9899999999974</v>
+        <v>497.0399999999952</v>
       </c>
       <c r="M99" t="n">
-        <v>500.3099999999974</v>
+        <v>499.5599999999952</v>
       </c>
       <c r="N99" t="n">
-        <v>497.9899999999974</v>
+        <v>497.0399999999952</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -5225,37 +5225,37 @@
         <v>98</v>
       </c>
       <c r="F100" t="n">
+        <v>44</v>
+      </c>
+      <c r="G100" t="n">
         <v>2</v>
-      </c>
-      <c r="G100" t="n">
-        <v>0</v>
       </c>
       <c r="H100" t="n">
         <v>490</v>
       </c>
       <c r="I100" t="n">
-        <v>491.5</v>
+        <v>494.6</v>
       </c>
       <c r="J100" t="n">
-        <v>491.5</v>
+        <v>494.6</v>
       </c>
       <c r="K100" t="n">
         <v>0</v>
       </c>
       <c r="L100" t="n">
-        <v>497.35</v>
+        <v>501.11</v>
       </c>
       <c r="M100" t="n">
-        <v>499.19</v>
+        <v>503.63</v>
       </c>
       <c r="N100" t="n">
-        <v>497.35</v>
+        <v>501.11</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -5273,7 +5273,7 @@
         <v>99</v>
       </c>
       <c r="F101" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G101" t="n">
         <v>3</v>
@@ -5303,7 +5303,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -5321,37 +5321,37 @@
         <v>100</v>
       </c>
       <c r="F102" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="G102" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H102" t="n">
         <v>500</v>
       </c>
       <c r="I102" t="n">
-        <v>501.5</v>
+        <v>503.05</v>
       </c>
       <c r="J102" t="n">
-        <v>505.1299999999974</v>
+        <v>503.05</v>
       </c>
       <c r="K102" t="n">
-        <v>3.629999999997381</v>
+        <v>0</v>
       </c>
       <c r="L102" t="n">
-        <v>511.4399999999974</v>
+        <v>508.9</v>
       </c>
       <c r="M102" t="n">
-        <v>513.7599999999974</v>
+        <v>510.74</v>
       </c>
       <c r="N102" t="n">
-        <v>511.4399999999974</v>
+        <v>508.9</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -5369,37 +5369,37 @@
         <v>101</v>
       </c>
       <c r="F103" t="n">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="G103" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H103" t="n">
         <v>505</v>
       </c>
       <c r="I103" t="n">
-        <v>506.5</v>
+        <v>508.05</v>
       </c>
       <c r="J103" t="n">
-        <v>513.7599999999948</v>
+        <v>510.7399999999951</v>
       </c>
       <c r="K103" t="n">
-        <v>7.259999999994761</v>
+        <v>2.689999999995052</v>
       </c>
       <c r="L103" t="n">
-        <v>520.2699999999948</v>
+        <v>516.5599999999951</v>
       </c>
       <c r="M103" t="n">
-        <v>522.7899999999947</v>
+        <v>518.3899999999951</v>
       </c>
       <c r="N103" t="n">
-        <v>529.3</v>
+        <v>524.2099999999928</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Random Median seed=15</t>
+          <t>Random Median seed=2</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -5417,31 +5417,31 @@
         <v>101</v>
       </c>
       <c r="F104" t="n">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="G104" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H104" t="n">
         <v>510</v>
       </c>
       <c r="I104" t="n">
-        <v>511.5</v>
+        <v>513.05</v>
       </c>
       <c r="J104" t="n">
-        <v>522.78999999999</v>
+        <v>518.3899999999927</v>
       </c>
       <c r="K104" t="n">
-        <v>11.28999999998996</v>
+        <v>5.339999999992756</v>
       </c>
       <c r="L104" t="n">
-        <v>529.3</v>
+        <v>524.2099999999928</v>
       </c>
       <c r="M104" t="n">
-        <v>531.8199999999899</v>
+        <v>526.0399999999927</v>
       </c>
       <c r="N104" t="n">
-        <v>529.3</v>
+        <v>524.2099999999928</v>
       </c>
     </row>
   </sheetData>
